--- a/frontend/references/화면정의서.xlsx
+++ b/frontend/references/화면정의서.xlsx
@@ -132,7 +132,7 @@
     <x:t xml:space="preserve">홈 대시보드</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">예산·재고·추천·성과·최근 지출 요약</x:t>
+    <x:t xml:space="preserve">예산·재고·추천·성과·최근 지출·지금 싼 재료(시세추천) 요약</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">로그인/예산 설정 완료</x:t>
@@ -285,7 +285,7 @@
     <x:t xml:space="preserve">장바구니</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">부족 재료 합산·가격·예산 비교</x:t>
+    <x:t xml:space="preserve">부족 재료 합산·가격·예산 비교·지금 싼 재료 추천</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">추천에서 장보기 목록 만들기 / 전역 장바구니</x:t>
@@ -444,10 +444,10 @@
     <x:t xml:space="preserve">가격</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">핫딜·시세</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">저렴한 재료·할인율·관련 레시피 제공</x:t>
+    <x:t xml:space="preserve">핫딜</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">오아시스 타임/마감세일·할인율·관련 레시피 제공</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">홈 뭐 사지 / P1 메뉴</x:t>
@@ -456,7 +456,7 @@
     <x:t xml:space="preserve">장바구니 추가 또는 외부 상품 이동</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">지마켓 타임딜 포함</x:t>
+    <x:t xml:space="preserve">오아시스 타임세일(15시)·마감세일(17시) / 시세추천은 홈·장바구니 임베드</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">SCR-022</x:t>
